--- a/assessment_forms/015_vlan_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/015_vlan_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vlan_configuration</t>
+          <t>assessment_results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VLAN configuration</t>
+          <t>Assessment results</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,41 +612,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>network_issues</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Network issues</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assessment_results</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assessment results</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>network_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>vlan_knowledge_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>VLAN comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>additional_comments_2</t>
+          <t>config_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Config Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>readiness_2</t>
+          <t>vlan_setup_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Readiness</t>
+          <t>VLAN setup comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assessment_results_2</t>
+          <t>network_topo_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assessment results</t>
+          <t>Network topology comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>network_topology_2</t>
+          <t>additional_comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Network topology</t>
+          <t>Additional comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vlan_config_comments</t>
+          <t>readiness_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Readiness comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,251 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vlan_setup_2</t>
+          <t>knowledge_questions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VLAN setup</t>
+          <t>Knowledge questions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>network_topo_comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>vlan_config_comments</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>vlan_config_comments_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>vlan_config_questions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>VLAN questions</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>vlan_questions</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>VLAN questions</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>vlan_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>vlan_questions_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>VLAN questions</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>config_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>vlan_knowledge_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>knowledge_questions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Knowledge questions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +896,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vlan_setup_choices</t>
+          <t>configuration_questions_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>what_is_the_main_purpose_of_vlan_configuration?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>What is the main purpose of VLAN configuration?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vlan_setup_choices</t>
+          <t>configuration_questions_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>what_is_the_difference_between_a_vlan_and_a_lan?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>What is the difference between a VLAN and a LAN?</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vlan_setup_choices</t>
+          <t>configuration_questions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>what_are_the_benefits_of_using_vlans?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>What are the benefits of using VLANs?</t>
         </is>
       </c>
     </row>
@@ -1182,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>how_do_you_set_up_a_new_vlan_in_your_network?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>How do you set up a new VLAN in your network?</t>
         </is>
       </c>
     </row>
@@ -1199,29 +969,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>what_are_the_common_vlan_setup_mistakes_to_avoid?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>What are the common VLAN setup mistakes to avoid?</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assessment_results_choices</t>
+          <t>vlan_setup_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>how_do_you_configure_vlan_trunking?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>How do you configure VLAN trunking?</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1003,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>readiness_choices</t>
+          <t>assessment_results_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_ready</t>
+          <t>fail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very ready</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>somewhat_ready</t>
+          <t>very_ready</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Somewhat ready</t>
+          <t>Very ready</t>
         </is>
       </c>
     </row>
@@ -1284,216 +1054,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_ready</t>
+          <t>somewhat_ready</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Not ready</t>
+          <t>Somewhat ready</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>comments_choices</t>
+          <t>readiness_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>not_ready</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>comments_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>fail</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>readiness_2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>very_ready</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Very ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>readiness_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>somewhat_ready</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Somewhat ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>readiness_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>not_ready</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>Not ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>assessment_results_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>assessment_results_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fail</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>vlan_setup_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>vlan_setup_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>vlan_setup_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vlan_setup_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>vlan_setup_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
     </row>
